--- a/МО 19.10.2026/Аудит переноса данных МО 19.10.2026.xlsx
+++ b/МО 19.10.2026/Аудит переноса данных МО 19.10.2026.xlsx
@@ -521,10 +521,10 @@
         <v>2220</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1968</v>
+        <v>1965</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -661,10 +661,10 @@
         <v>1793</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1572</v>
+        <v>1575</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
@@ -1361,22 +1361,22 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.87, Петина Ирина Викторовна; подразделение</t>
+          <t>Учёт, стр.8, Ястребов Александр Сергеевич; подразделение</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Склад (МШ н/д)</t>
+          <t>Отдел технического контроля М</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Склад</t>
+          <t>Отдел технического контроля</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -1393,22 +1393,22 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.88, Рузайкин Юрий Андреевич; подразделение</t>
+          <t>Учёт, стр.10, Ермакова Наталья Васильевна; подразделение</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел Р</t>
+          <t>Отдел технического контроля М</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел</t>
+          <t>Отдел технического контроля</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -1425,22 +1425,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.89, Хлыщенко Александр Александрович; подразделение</t>
+          <t>Учёт, стр.11, Шрамко Наталья Викторовна; подразделение</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел МШ</t>
+          <t>Отдел технического контроля М</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел</t>
+          <t>Отдел технического контроля</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -1457,22 +1457,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.90, Абрамович Светлана Николаевна; подразделение</t>
+          <t>Учёт, стр.87, Петина Ирина Викторовна; подразделение</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел МШ</t>
+          <t>Склад (МШ н/д)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.91, Баранникова Елена Александровна; подразделение</t>
+          <t>Учёт, стр.88, Рузайкин Юрий Андреевич; подразделение</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел МШ</t>
+          <t>Планово-диспетчерский отдел Р</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.92, Гришин Алексей Владимирович; подразделение</t>
+          <t>Учёт, стр.89, Хлыщенко Александр Александрович; подразделение</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.93, Зубехин Григорий Александрович; подразделение</t>
+          <t>Учёт, стр.90, Абрамович Светлана Николаевна; подразделение</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.94, Кадиева Наталья Борисовна; подразделение</t>
+          <t>Учёт, стр.91, Баранникова Елена Александровна; подразделение</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.95, Лапкин Виталий Олегович; подразделение</t>
+          <t>Учёт, стр.92, Гришин Алексей Владимирович; подразделение</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.96, Лапкина Анастасия Владимировна; подразделение</t>
+          <t>Учёт, стр.93, Зубехин Григорий Александрович; подразделение</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.97, Гришина Неля Евгеньевна; подразделение</t>
+          <t>Учёт, стр.94, Кадиева Наталья Борисовна; подразделение</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.98, Запотылок Алена Владимировна; подразделение</t>
+          <t>Учёт, стр.95, Лапкин Виталий Олегович; подразделение</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.99, Паукова Наталья Владимировна; подразделение</t>
+          <t>Учёт, стр.96, Лапкина Анастасия Владимировна; подразделение</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.100, Полозов Василий Борисович; подразделение</t>
+          <t>Учёт, стр.97, Гришина Неля Евгеньевна; подразделение</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.101, Попова Юлия Александровна; подразделение</t>
+          <t>Учёт, стр.98, Запотылок Алена Владимировна; подразделение</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.102, Агапов Максим Владимирович; подразделение</t>
+          <t>Учёт, стр.99, Паукова Наталья Владимировна; подразделение</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Планово-диспетчерский отдел МШ</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Механический участок</t>
+          <t>Планово-диспетчерский отдел</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.103, Артёмов Антон Анатольевич; подразделение</t>
+          <t>Учёт, стр.100, Полозов Василий Борисович; подразделение</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Планово-диспетчерский отдел МШ</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Механический участок</t>
+          <t>Планово-диспетчерский отдел</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -1905,22 +1905,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.104, Потапкин Илья Анатольевич; подразделение</t>
+          <t>Учёт, стр.101, Попова Юлия Александровна; подразделение</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Планово-диспетчерский отдел МШ</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Механический участок</t>
+          <t>Планово-диспетчерский отдел</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.105, Назин Владислав Сергеевич; подразделение</t>
+          <t>Учёт, стр.102, Агапов Максим Владимирович; подразделение</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.106, Орлов Михаил Юрьевич; подразделение</t>
+          <t>Учёт, стр.103, Артёмов Антон Анатольевич; подразделение</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.107, Тарасов Борис Анатольевич; подразделение</t>
+          <t>Учёт, стр.104, Потапкин Илья Анатольевич; подразделение</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.108, Фокина Светлана Геннадиевна; подразделение</t>
+          <t>Учёт, стр.105, Назин Владислав Сергеевич; подразделение</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.109, Бондин Денис Игоревич; подразделение</t>
+          <t>Учёт, стр.106, Орлов Михаил Юрьевич; подразделение</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.110, Саранцев Петр Дмитриевич; подразделение</t>
+          <t>Учёт, стр.107, Тарасов Борис Анатольевич; подразделение</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.111, Юдаков Алексей Викторович; подразделение</t>
+          <t>Учёт, стр.108, Фокина Светлана Геннадиевна; подразделение</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.112, Клюг Андрей Эдуардович; подразделение</t>
+          <t>Учёт, стр.109, Бондин Денис Игоревич; подразделение</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2193,22 +2193,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.113, Бугаев Сергей Петрович; подразделение</t>
+          <t>Учёт, стр.110, Саранцев Петр Дмитриевич; подразделение</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Слесарный участок МШ</t>
+          <t>Механический участок МШ</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Слесарный участок</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2225,22 +2225,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.114, Макаренков Святослав Михайлович; подразделение</t>
+          <t>Учёт, стр.111, Юдаков Алексей Викторович; подразделение</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Слесарный участок МШ</t>
+          <t>Механический участок МШ</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Слесарный участок</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2257,22 +2257,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.115, Савичев Сергей Сергеевич; подразделение</t>
+          <t>Учёт, стр.112, Клюг Андрей Эдуардович; подразделение</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Слесарный участок МШ</t>
+          <t>Механический участок МШ</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Слесарный участок</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.116, Сафонов Роман Валерьевич; подразделение</t>
+          <t>Учёт, стр.113, Бугаев Сергей Петрович; подразделение</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.117, Филимонов Андрей Владимирович; подразделение</t>
+          <t>Учёт, стр.114, Макаренков Святослав Михайлович; подразделение</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.118, Епифанов Александр Сергеевич; подразделение</t>
+          <t>Учёт, стр.115, Савичев Сергей Сергеевич; подразделение</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.119, Семененко Александр Михайлович; подразделение</t>
+          <t>Учёт, стр.116, Сафонов Роман Валерьевич; подразделение</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.120, Сорокин Игорь Анатольевич; подразделение</t>
+          <t>Учёт, стр.117, Филимонов Андрей Владимирович; подразделение</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2449,22 +2449,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.121, Горелов Андрей Сергеевич; подразделение</t>
+          <t>Учёт, стр.118, Епифанов Александр Сергеевич; подразделение</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Слесарный участок МШ</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Механический участок</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2481,22 +2481,22 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.122, Зинченко Денис Андреевич; подразделение</t>
+          <t>Учёт, стр.119, Семененко Александр Михайлович; подразделение</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Слесарный участок МШ</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Механический участок</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2513,22 +2513,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.123, Кулешов Руслан Викторович; подразделение</t>
+          <t>Учёт, стр.120, Сорокин Игорь Анатольевич; подразделение</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Слесарный участок МШ</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Механический участок</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.124, Нагаев Дмитрий Александрович; подразделение</t>
+          <t>Учёт, стр.121, Горелов Андрей Сергеевич; подразделение</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2577,22 +2577,22 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.125, Виноградов Валерий Валерьевич; подразделение</t>
+          <t>Учёт, стр.122, Зинченко Денис Андреевич; подразделение</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Слесарный участок МШ</t>
+          <t>Механический участок МШ</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Слесарный участок</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2609,22 +2609,22 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.126, Карантышов Андрей Витальевич; подразделение</t>
+          <t>Учёт, стр.123, Кулешов Руслан Викторович; подразделение</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Слесарный участок МШ</t>
+          <t>Механический участок МШ</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Слесарный участок</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2641,22 +2641,22 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.127, Рыскин Вадим Вячеславович; подразделение</t>
+          <t>Учёт, стр.124, Нагаев Дмитрий Александрович; подразделение</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Слесарный участок МШ</t>
+          <t>Механический участок МШ</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Слесарный участок</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.128, Терёхин Кирилл Павлович; подразделение</t>
+          <t>Учёт, стр.125, Виноградов Валерий Валерьевич; подразделение</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2705,22 +2705,22 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.129, Кокорев Анатолий Сергеевич; подразделение</t>
+          <t>Учёт, стр.126, Карантышов Андрей Витальевич; подразделение</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Участок РЭО МШ</t>
+          <t>Слесарный участок МШ</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Участок РЭО</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2737,22 +2737,22 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.130, Богданов Александр Викторович; подразделение</t>
+          <t>Учёт, стр.127, Рыскин Вадим Вячеславович; подразделение</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Участок РЭО МШ</t>
+          <t>Слесарный участок МШ</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Участок РЭО</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2769,22 +2769,22 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.131, Озорнов Игорь Валерьевич; подразделение</t>
+          <t>Учёт, стр.128, Терёхин Кирилл Павлович; подразделение</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Участок РЭО МШ</t>
+          <t>Слесарный участок МШ</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Участок РЭО</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.132, Романов Дмитрий Евгеньевич; подразделение</t>
+          <t>Учёт, стр.129, Кокорев Анатолий Сергеевич; подразделение</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.133, Шабалин Александр Сергеевич; подразделение</t>
+          <t>Учёт, стр.130, Богданов Александр Викторович; подразделение</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2865,22 +2865,22 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.134, Бабенко Олег Анатольевич; подразделение</t>
+          <t>Учёт, стр.131, Озорнов Игорь Валерьевич; подразделение</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Участок РЭО МШ</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Мебельный участок</t>
+          <t>Участок РЭО</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2897,22 +2897,22 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.135, Макарский Станислав Иванович; подразделение</t>
+          <t>Учёт, стр.132, Романов Дмитрий Евгеньевич; подразделение</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Участок РЭО МШ</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Мебельный участок</t>
+          <t>Участок РЭО</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2929,22 +2929,22 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.136, Мураев Вадим Викторович; подразделение</t>
+          <t>Учёт, стр.133, Шабалин Александр Сергеевич; подразделение</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Участок РЭО МШ</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Мебельный участок</t>
+          <t>Участок РЭО</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.137, Алманов Вячеслав Михайлович; подразделение</t>
+          <t>Учёт, стр.134, Бабенко Олег Анатольевич; подразделение</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.138, Кротков Александр Юрьевич; подразделение</t>
+          <t>Учёт, стр.135, Макарский Станислав Иванович; подразделение</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.139, Семенов Александр Александрович; подразделение</t>
+          <t>Учёт, стр.136, Мураев Вадим Викторович; подразделение</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.140, Морозов Олег Валерьевич; подразделение</t>
+          <t>Учёт, стр.137, Алманов Вячеслав Михайлович; подразделение</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.141, Нерозников Роман Анатольевич; подразделение</t>
+          <t>Учёт, стр.138, Кротков Александр Юрьевич; подразделение</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.142, Никитин Валерий Сергеевич; подразделение</t>
+          <t>Учёт, стр.139, Семенов Александр Александрович; подразделение</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.143, Бутузов Вадим Владимирович; подразделение</t>
+          <t>Учёт, стр.140, Морозов Олег Валерьевич; подразделение</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.144, Анненков Олег Викторович; подразделение</t>
+          <t>Учёт, стр.141, Нерозников Роман Анатольевич; подразделение</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.145, Захаров Юрий Викторович; подразделение</t>
+          <t>Учёт, стр.142, Никитин Валерий Сергеевич; подразделение</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.146, Малышкин Сергей Константинович; подразделение</t>
+          <t>Учёт, стр.143, Бутузов Вадим Владимирович; подразделение</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.147, Маркарян Роман Рубикович; подразделение</t>
+          <t>Учёт, стр.144, Анненков Олег Викторович; подразделение</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.148, Савельев Станислав Юрьевич; подразделение</t>
+          <t>Учёт, стр.145, Захаров Юрий Викторович; подразделение</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.149, Селиванов Алексей Алексеевич; подразделение</t>
+          <t>Учёт, стр.146, Малышкин Сергей Константинович; подразделение</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.150, Трушков Сергей Викторович; подразделение</t>
+          <t>Учёт, стр.147, Маркарян Роман Рубикович; подразделение</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.151, Черносвитов Дмитрий Львович; подразделение</t>
+          <t>Учёт, стр.148, Савельев Станислав Юрьевич; подразделение</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.152, Кукушкин Дмитрий Вячеславович; подразделение</t>
+          <t>Учёт, стр.149, Селиванов Алексей Алексеевич; подразделение</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.153, Михиенков Валерий Евгеньевич; подразделение</t>
+          <t>Учёт, стр.150, Трушков Сергей Викторович; подразделение</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.154, Петушков Дмитрий Сергеевич; подразделение</t>
+          <t>Учёт, стр.151, Черносвитов Дмитрий Львович; подразделение</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.155, Полудкин Роман Владимирович; подразделение</t>
+          <t>Учёт, стр.152, Кукушкин Дмитрий Вячеславович; подразделение</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.156, Рыжков Олег Николаевич; подразделение</t>
+          <t>Учёт, стр.153, Михиенков Валерий Евгеньевич; подразделение</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.157, Степанов Валентин Владимирович; подразделение</t>
+          <t>Учёт, стр.154, Петушков Дмитрий Сергеевич; подразделение</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.158, Цибин Николай Дмитриевич; подразделение</t>
+          <t>Учёт, стр.155, Полудкин Роман Владимирович; подразделение</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.159, Шеин Андрей Геннадьевич; подразделение</t>
+          <t>Учёт, стр.156, Рыжков Олег Николаевич; подразделение</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.160, Балалаев Сергей Викторович; подразделение</t>
+          <t>Учёт, стр.157, Степанов Валентин Владимирович; подразделение</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.161, Матухно Константин Викторович; подразделение</t>
+          <t>Учёт, стр.158, Цибин Николай Дмитриевич; подразделение</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.162, Анисимов Игорь Владимирович; подразделение</t>
+          <t>Учёт, стр.159, Шеин Андрей Геннадьевич; подразделение</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.163, Кукушкин Максим Дмитриевич; подразделение</t>
+          <t>Учёт, стр.160, Балалаев Сергей Викторович; подразделение</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.164, Антропов Иван Юрьевич; подразделение</t>
+          <t>Учёт, стр.161, Матухно Константин Викторович; подразделение</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.165, Ветлянский Александр Александрович; подразделение</t>
+          <t>Учёт, стр.162, Анисимов Игорь Владимирович; подразделение</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.166, Арифулин Александр Александрович; подразделение</t>
+          <t>Учёт, стр.163, Кукушкин Максим Дмитриевич; подразделение</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.167, Пантюхов Вячеслав Владимирович; подразделение</t>
+          <t>Учёт, стр.164, Антропов Иван Юрьевич; подразделение</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.168, Хасянов Ильфат Шамильевич; подразделение</t>
+          <t>Учёт, стр.165, Ветлянский Александр Александрович; подразделение</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.169, Бредихин Евгений Васильевич; подразделение</t>
+          <t>Учёт, стр.166, Арифулин Александр Александрович; подразделение</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.170, Зайцев Андрей Александрович; подразделение</t>
+          <t>Учёт, стр.167, Пантюхов Вячеслав Владимирович; подразделение</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.171, Пичугин Александр Владимирович; подразделение</t>
+          <t>Учёт, стр.168, Хасянов Ильфат Шамильевич; подразделение</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.172, Тимошенко Александр Олегович; подразделение</t>
+          <t>Учёт, стр.169, Бредихин Евгений Васильевич; подразделение</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4113,7 +4113,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.173, Чусов Иван Леонидович; подразделение</t>
+          <t>Учёт, стр.170, Зайцев Андрей Александрович; подразделение</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4145,22 +4145,22 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.174, Попов Виктор Михайлович; подразделение</t>
+          <t>Учёт, стр.171, Пичугин Александр Владимирович; подразделение</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Мебельный участок МШ</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4177,22 +4177,22 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.175, Габбасов Евгений Рафисович; подразделение</t>
+          <t>Учёт, стр.172, Тимошенко Александр Олегович; подразделение</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Мебельный участок МШ</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4209,22 +4209,22 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.176, Калинкин Анатолий Сергеевич; подразделение</t>
+          <t>Учёт, стр.173, Чусов Иван Леонидович; подразделение</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Мебельный участок МШ</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.177, Морев Александр Михайлович; подразделение</t>
+          <t>Учёт, стр.174, Попов Виктор Михайлович; подразделение</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.178, Морев Владимир Александрович; подразделение</t>
+          <t>Учёт, стр.175, Габбасов Евгений Рафисович; подразделение</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.179, Первушин Максим Александрович; подразделение</t>
+          <t>Учёт, стр.176, Калинкин Анатолий Сергеевич; подразделение</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.180, Солодков Максим Юрьевич; подразделение</t>
+          <t>Учёт, стр.177, Морев Александр Михайлович; подразделение</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.181, Алманова Дойна Виореловна; подразделение</t>
+          <t>Учёт, стр.178, Морев Владимир Александрович; подразделение</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.182, Долинская Валерия Александровна; подразделение</t>
+          <t>Учёт, стр.179, Первушин Максим Александрович; подразделение</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.183, Симонова Виктория Александровна; подразделение</t>
+          <t>Учёт, стр.180, Солодков Максим Юрьевич; подразделение</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.184, Тимохин Александр Владимирович; подразделение</t>
+          <t>Учёт, стр.181, Алманова Дойна Виореловна; подразделение</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.185, Караваев Игорь Александрович; подразделение</t>
+          <t>Учёт, стр.182, Долинская Валерия Александровна; подразделение</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.186, Лисовский Александр Валерьевич; подразделение</t>
+          <t>Учёт, стр.183, Симонова Виктория Александровна; подразделение</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.187, Лысенко Анатолий Алексеевич; подразделение</t>
+          <t>Учёт, стр.184, Тимохин Александр Владимирович; подразделение</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.188, Никитин Марат Николаевич; подразделение</t>
+          <t>Учёт, стр.185, Караваев Игорь Александрович; подразделение</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.189, Ожерельев Сергей Николаевич; подразделение</t>
+          <t>Учёт, стр.186, Лисовский Александр Валерьевич; подразделение</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4657,7 +4657,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.190, Гимадиев Евгений Искандерович; подразделение</t>
+          <t>Учёт, стр.187, Лысенко Анатолий Алексеевич; подразделение</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.191, Китов Алексей Геннадьевич; подразделение</t>
+          <t>Учёт, стр.188, Никитин Марат Николаевич; подразделение</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4721,7 +4721,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.192, Тишин Алексей Владимирович; подразделение</t>
+          <t>Учёт, стр.189, Ожерельев Сергей Николаевич; подразделение</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.193, Пухова Жанна Аслановна; подразделение</t>
+          <t>Учёт, стр.190, Гимадиев Евгений Искандерович; подразделение</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4785,22 +4785,22 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.194, Иванов Андрей Петрович; подразделение</t>
+          <t>Учёт, стр.191, Китов Алексей Геннадьевич; подразделение</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Служба главного инженера МШ</t>
+          <t>Участок декоративной отделки МШ</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Служба главного инженера</t>
+          <t>Участок декоративной отделки</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.195, Божьева Ирина Вячеславовна; подразделение</t>
+          <t>Учёт, стр.192, Тишин Алексей Владимирович; подразделение</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Отдел технического контроля МШ</t>
+          <t>Участок декоративной отделки МШ</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Отдел технического контроля</t>
+          <t>Участок декоративной отделки</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4849,22 +4849,22 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.196, Васильева Алина Владимировна; подразделение</t>
+          <t>Учёт, стр.193, Пухова Жанна Аслановна; подразделение</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Отдел технического контроля МШ</t>
+          <t>Участок декоративной отделки МШ</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Отдел технического контроля</t>
+          <t>Участок декоративной отделки</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4881,22 +4881,22 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.197, Райкова Ирина Алексеевна; подразделение</t>
+          <t>Учёт, стр.194, Иванов Андрей Петрович; подразделение</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Отдел технического контроля МШ</t>
+          <t>Служба главного инженера МШ</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Отдел технического контроля</t>
+          <t>Служба главного инженера</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4913,22 +4913,22 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.198, Трушаков Владимир Александрович; подразделение</t>
+          <t>Учёт, стр.195, Божьева Ирина Вячеславовна; подразделение</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Служба главного инженера МШ</t>
+          <t>Отдел технического контроля МШ</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Служба главного инженера</t>
+          <t>Отдел технического контроля</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4945,22 +4945,22 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.199, Иванов Владимир Максимович; подразделение</t>
+          <t>Учёт, стр.196, Васильева Алина Владимировна; подразделение</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Служба главного инженера МШ</t>
+          <t>Отдел технического контроля МШ</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Служба главного инженера</t>
+          <t>Отдел технического контроля</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -4977,22 +4977,22 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.200, Найденов Андрей Александрович; подразделение</t>
+          <t>Учёт, стр.197, Райкова Ирина Алексеевна; подразделение</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Служба главного инженера МШ</t>
+          <t>Отдел технического контроля МШ</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Служба главного инженера</t>
+          <t>Отдел технического контроля</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.201, Королев Владислав Владимирович; подразделение</t>
+          <t>Учёт, стр.198, Трушаков Владимир Александрович; подразделение</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.202, Омельченко Вячеслав Васильевич; подразделение</t>
+          <t>Учёт, стр.199, Иванов Владимир Максимович; подразделение</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.203, Калинин Дмитрий Александрович; подразделение</t>
+          <t>Учёт, стр.200, Найденов Андрей Александрович; подразделение</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5105,7 +5105,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.204, Старовойтов Владимир Владимирович; подразделение</t>
+          <t>Учёт, стр.201, Королев Владислав Владимирович; подразделение</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.205, Долженко Александр Сергеевич; подразделение</t>
+          <t>Учёт, стр.202, Омельченко Вячеслав Васильевич; подразделение</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.206, Климов Дмитрий Николаевич; подразделение</t>
+          <t>Учёт, стр.203, Калинин Дмитрий Александрович; подразделение</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.207, Кармазин Александр Николаевич; подразделение</t>
+          <t>Учёт, стр.204, Старовойтов Владимир Владимирович; подразделение</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.208, Бизюков Сергей Иванович; подразделение</t>
+          <t>Учёт, стр.205, Долженко Александр Сергеевич; подразделение</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.209, Хромов Павел Николаевич; подразделение</t>
+          <t>Учёт, стр.206, Климов Дмитрий Николаевич; подразделение</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.210, Жусев Алексей Анатольевич; подразделение</t>
+          <t>Учёт, стр.207, Кармазин Александр Николаевич; подразделение</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.211, Грачев Андрей Николаевич; подразделение</t>
+          <t>Учёт, стр.208, Бизюков Сергей Иванович; подразделение</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5361,22 +5361,22 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.212, Захарова Любовь Владимировна; подразделение</t>
+          <t>Учёт, стр.209, Хромов Павел Николаевич; подразделение</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел МШ</t>
+          <t>Служба главного инженера МШ</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел</t>
+          <t>Служба главного инженера</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5393,22 +5393,22 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.213, Гросс Елена Владимировна; подразделение</t>
+          <t>Учёт, стр.210, Жусев Алексей Анатольевич; подразделение</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел МШ</t>
+          <t>Служба главного инженера МШ</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел</t>
+          <t>Служба главного инженера</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5425,22 +5425,22 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.214, Декун Лидия Петровна; подразделение</t>
+          <t>Учёт, стр.211, Грачев Андрей Николаевич; подразделение</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел МШ</t>
+          <t>Служба главного инженера МШ</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел</t>
+          <t>Служба главного инженера</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.215, Михеева Наталия Петровна; подразделение</t>
+          <t>Учёт, стр.212, Захарова Любовь Владимировна; подразделение</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5489,7 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.216, Новоторцева Наталия Николаевна; подразделение</t>
+          <t>Учёт, стр.213, Гросс Елена Владимировна; подразделение</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.217, Савичева Марина Анатольевна; подразделение</t>
+          <t>Учёт, стр.214, Декун Лидия Петровна; подразделение</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.218, Хилинская Анна Александровна; подразделение</t>
+          <t>Учёт, стр.215, Михеева Наталия Петровна; подразделение</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5585,22 +5585,22 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.219, Беспалов Виталий Анатольевич; подразделение</t>
+          <t>Учёт, стр.216, Новоторцева Наталия Николаевна; подразделение</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Отдел режима МШ</t>
+          <t>Административно-хозяйственный отдел МШ</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Отдел режима</t>
+          <t>Административно-хозяйственный отдел</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5617,22 +5617,22 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.220, Волгин Анатолий Иванович; подразделение</t>
+          <t>Учёт, стр.217, Савичева Марина Анатольевна; подразделение</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Отдел режима МШ</t>
+          <t>Административно-хозяйственный отдел МШ</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Отдел режима</t>
+          <t>Административно-хозяйственный отдел</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5649,22 +5649,22 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.221, Гусев Александр Николаевич; подразделение</t>
+          <t>Учёт, стр.218, Хилинская Анна Александровна; подразделение</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Отдел режима МШ</t>
+          <t>Административно-хозяйственный отдел МШ</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Отдел режима</t>
+          <t>Административно-хозяйственный отдел</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.222, Дудукин Сергей Вячеславович; подразделение</t>
+          <t>Учёт, стр.219, Беспалов Виталий Анатольевич; подразделение</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.223, Звягин Евгений Иванович; подразделение</t>
+          <t>Учёт, стр.220, Волгин Анатолий Иванович; подразделение</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.224, Макаренко Алексей Иванович; подразделение</t>
+          <t>Учёт, стр.221, Гусев Александр Николаевич; подразделение</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.225, Матвицкий Виктор Владимирович; подразделение</t>
+          <t>Учёт, стр.222, Дудукин Сергей Вячеславович; подразделение</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.226, Камбулатов Эсенбулат Камбулатович; подразделение</t>
+          <t>Учёт, стр.223, Звягин Евгений Иванович; подразделение</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.227, Рукин Денис Игоревич; подразделение</t>
+          <t>Учёт, стр.224, Макаренко Алексей Иванович; подразделение</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5873,22 +5873,22 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.228, Балкивская Людмила Алексеевна; подразделение</t>
+          <t>Учёт, стр.225, Матвицкий Виктор Владимирович; подразделение</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Склад МШ</t>
+          <t>Отдел режима МШ</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Склад</t>
+          <t>Отдел режима</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5905,22 +5905,22 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.229, Карпачева Татьяна Владимировна; подразделение</t>
+          <t>Учёт, стр.226, Камбулатов Эсенбулат Камбулатович; подразделение</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Склад МШ</t>
+          <t>Отдел режима МШ</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Склад</t>
+          <t>Отдел режима</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5937,22 +5937,22 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.230, Нестеров Аркадий Николаевич; подразделение</t>
+          <t>Учёт, стр.227, Рукин Денис Игоревич; подразделение</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Склад МШ</t>
+          <t>Отдел режима МШ</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Склад</t>
+          <t>Отдел режима</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.231, Густов Александр Витальевич; подразделение</t>
+          <t>Учёт, стр.228, Балкивская Людмила Алексеевна; подразделение</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.232, Дягин Александр Александрович; подразделение</t>
+          <t>Учёт, стр.229, Карпачева Татьяна Владимировна; подразделение</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.233, Евменчук Елизавета Александровна; подразделение</t>
+          <t>Учёт, стр.230, Нестеров Аркадий Николаевич; подразделение</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.234, Ноженко Екатерина Сергеевна; подразделение</t>
+          <t>Учёт, стр.231, Густов Александр Витальевич; подразделение</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.235, Прохорова Маргарита Александровна; подразделение</t>
+          <t>Учёт, стр.232, Дягин Александр Александрович; подразделение</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.236, Султанов Тимур Боирович; подразделение</t>
+          <t>Учёт, стр.233, Евменчук Елизавета Александровна; подразделение</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.237, Богатырев Николай Владимирович; подразделение</t>
+          <t>Учёт, стр.234, Ноженко Екатерина Сергеевна; подразделение</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.238, Агалиев Рафаэл Рашидович; подразделение</t>
+          <t>Учёт, стр.235, Прохорова Маргарита Александровна; подразделение</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.239, Каменев Дмитрий Викторович; подразделение</t>
+          <t>Учёт, стр.236, Султанов Тимур Боирович; подразделение</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.240, Ласкавый Андрей Викторович; подразделение</t>
+          <t>Учёт, стр.237, Богатырев Николай Владимирович; подразделение</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6289,7 +6289,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.241, Моряков Константин Викторович; подразделение</t>
+          <t>Учёт, стр.238, Агалиев Рафаэл Рашидович; подразделение</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.242, Хохлов Александр Николаевич; подразделение</t>
+          <t>Учёт, стр.239, Каменев Дмитрий Викторович; подразделение</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.243, Кирбенева Татьяна Александровна; подразделение</t>
+          <t>Учёт, стр.240, Ласкавый Андрей Викторович; подразделение</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.244, Лягинова Анастасия Витальевна; подразделение</t>
+          <t>Учёт, стр.241, Моряков Константин Викторович; подразделение</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6417,22 +6417,22 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.245, Акимов Михаил Александрович; подразделение</t>
+          <t>Учёт, стр.242, Хохлов Александр Николаевич; подразделение</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Отдел транспортного обеспечения МШ</t>
+          <t>Склад МШ</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Отдел транспортного обеспечения</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6449,22 +6449,22 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.246, Батуревич Юрий Викторович; подразделение</t>
+          <t>Учёт, стр.243, Кирбенева Татьяна Александровна; подразделение</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Отдел транспортного обеспечения МШ</t>
+          <t>Склад МШ</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Отдел транспортного обеспечения</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6481,22 +6481,22 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.247, Василенко Александр Иванович; подразделение</t>
+          <t>Учёт, стр.244, Лягинова Анастасия Витальевна; подразделение</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Отдел транспортного обеспечения МШ</t>
+          <t>Склад МШ</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Отдел транспортного обеспечения</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.248, Грязнов Анатолий Николаевич; подразделение</t>
+          <t>Учёт, стр.245, Акимов Михаил Александрович; подразделение</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6545,7 +6545,7 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.249, Евдокимов Игорь Валентинович; подразделение</t>
+          <t>Учёт, стр.246, Батуревич Юрий Викторович; подразделение</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.250, Ерофеев Олег Игоревич; подразделение</t>
+          <t>Учёт, стр.247, Василенко Александр Иванович; подразделение</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.251, Жигунов Вячеслав Владимирович; подразделение</t>
+          <t>Учёт, стр.248, Грязнов Анатолий Николаевич; подразделение</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.252, Крутяков Сергей Владимирович; подразделение</t>
+          <t>Учёт, стр.249, Евдокимов Игорь Валентинович; подразделение</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.253, Лучкин Евгений Иванович; подразделение</t>
+          <t>Учёт, стр.250, Ерофеев Олег Игоревич; подразделение</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6705,22 +6705,22 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.288, Галимзянова Гузель Раисовна; подразделение</t>
+          <t>Учёт, стр.251, Жигунов Вячеслав Владимирович; подразделение</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел Р</t>
+          <t>Отдел транспортного обеспечения МШ</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел</t>
+          <t>Отдел транспортного обеспечения</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6737,22 +6737,22 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.289, Донин Алексей Валентинович; подразделение</t>
+          <t>Учёт, стр.252, Крутяков Сергей Владимирович; подразделение</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел Р</t>
+          <t>Отдел транспортного обеспечения МШ</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел</t>
+          <t>Отдел транспортного обеспечения</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6769,22 +6769,22 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.290, Иванова Светлана Васильевна; подразделение</t>
+          <t>Учёт, стр.253, Лучкин Евгений Иванович; подразделение</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел Р</t>
+          <t>Отдел транспортного обеспечения МШ</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>Административно-хозяйственный отдел</t>
+          <t>Отдел транспортного обеспечения</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.291, Раззакова Светлана Владимировна; подразделение</t>
+          <t>Учёт, стр.288, Галимзянова Гузель Раисовна; подразделение</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.292, Терешкина Татьяна Викторовна; подразделение</t>
+          <t>Учёт, стр.289, Донин Алексей Валентинович; подразделение</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.293, Шибатина Елена Васильевна; подразделение</t>
+          <t>Учёт, стр.290, Иванова Светлана Васильевна; подразделение</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6897,7 +6897,7 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.294, Болденкова Анна Сергеевна; подразделение</t>
+          <t>Учёт, стр.291, Раззакова Светлана Владимировна; подразделение</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6929,22 +6929,22 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.295, Улумбеков Руслан Бинарович; подразделение</t>
+          <t>Учёт, стр.292, Терешкина Татьяна Викторовна; подразделение</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Служба главного инженера Р</t>
+          <t>Административно-хозяйственный отдел Р</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Служба главного инженера</t>
+          <t>Административно-хозяйственный отдел</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6961,22 +6961,22 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.296, Гришин Алексей Валерьевич; подразделение</t>
+          <t>Учёт, стр.293, Шибатина Елена Васильевна; подразделение</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Слесарный участок Р</t>
+          <t>Административно-хозяйственный отдел Р</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>Слесарный участок</t>
+          <t>Административно-хозяйственный отдел</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -6993,22 +6993,22 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.297, Поливанов Иван Юрьевич; подразделение</t>
+          <t>Учёт, стр.294, Болденкова Анна Сергеевна; подразделение</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Механический участок Р</t>
+          <t>Административно-хозяйственный отдел Р</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Механический участок</t>
+          <t>Административно-хозяйственный отдел</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7025,22 +7025,22 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.298, Степанов Максим Анатольевич; подразделение</t>
+          <t>Учёт, стр.295, Улумбеков Руслан Бинарович; подразделение</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Механический участок Р</t>
+          <t>Служба главного инженера Р</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>Механический участок</t>
+          <t>Служба главного инженера</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.299, Янышев Тимур Ильгизович; подразделение</t>
+          <t>Учёт, стр.296, Гришин Алексей Валерьевич; подразделение</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Механический участок Р</t>
+          <t>Слесарный участок Р</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>Механический участок</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7089,7 +7089,7 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.300, Геращенко Сергей Владимирович; подразделение</t>
+          <t>Учёт, стр.297, Поливанов Иван Юрьевич; подразделение</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.301, Куликов Сергей Сергеевич; подразделение</t>
+          <t>Учёт, стр.298, Степанов Максим Анатольевич; подразделение</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.302, Пак Игорь Трофимович; подразделение</t>
+          <t>Учёт, стр.299, Янышев Тимур Ильгизович; подразделение</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7185,7 +7185,7 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.303, Герасимов Александр Александрович; подразделение</t>
+          <t>Учёт, стр.300, Геращенко Сергей Владимирович; подразделение</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.304, Кашкаров Сергей Евгеньевич; подразделение</t>
+          <t>Учёт, стр.301, Куликов Сергей Сергеевич; подразделение</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.305, Павозков Евгений Александрович; подразделение</t>
+          <t>Учёт, стр.302, Пак Игорь Трофимович; подразделение</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7281,22 +7281,22 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.306, Баев Сергей Александрович; подразделение</t>
+          <t>Учёт, стр.303, Герасимов Александр Александрович; подразделение</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Слесарный участок Р</t>
+          <t>Механический участок Р</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>Слесарный участок</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7313,22 +7313,22 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.307, Корнеев Виктор Николаевич; подразделение</t>
+          <t>Учёт, стр.304, Кашкаров Сергей Евгеньевич; подразделение</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Слесарный участок Р</t>
+          <t>Механический участок Р</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>Слесарный участок</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.308, Горнеев Никита Сергеевич; подразделение</t>
+          <t>Учёт, стр.305, Павозков Евгений Александрович; подразделение</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7377,22 +7377,22 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.309, Панков Иван Валерьевич; подразделение</t>
+          <t>Учёт, стр.306, Баев Сергей Александрович; подразделение</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Механический участок Р</t>
+          <t>Слесарный участок Р</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>Механический участок</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7409,22 +7409,22 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.310, Воркунов Егор Дмитриевич; подразделение</t>
+          <t>Учёт, стр.307, Корнеев Виктор Николаевич; подразделение</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Механический участок Р</t>
+          <t>Слесарный участок Р</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>Механический участок</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.311, Птицын Юрий Юрьевич; подразделение</t>
+          <t>Учёт, стр.308, Горнеев Никита Сергеевич; подразделение</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.312, Семячко Константин Григорьевич; подразделение</t>
+          <t>Учёт, стр.309, Панков Иван Валерьевич; подразделение</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.313, Андреев Кирилл Владимирович; подразделение</t>
+          <t>Учёт, стр.310, Воркунов Егор Дмитриевич; подразделение</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7537,22 +7537,22 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.314, Федышен Валерий Васильевич; подразделение</t>
+          <t>Учёт, стр.311, Птицын Юрий Юрьевич; подразделение</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Слесарный участок Р</t>
+          <t>Механический участок Р</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>Слесарный участок</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7569,22 +7569,22 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.315, Козлов Алексей Викторович; подразделение</t>
+          <t>Учёт, стр.312, Семячко Константин Григорьевич; подразделение</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Слесарный участок Р</t>
+          <t>Механический участок Р</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>Слесарный участок</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7601,22 +7601,22 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.316, Чепуштанов Александр Геннадьевич; подразделение</t>
+          <t>Учёт, стр.313, Андреев Кирилл Владимирович; подразделение</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Участок сборки Р</t>
+          <t>Механический участок Р</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>Участок сборки</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7633,22 +7633,22 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.317, Житников Андрей Николаевич; подразделение</t>
+          <t>Учёт, стр.314, Федышен Валерий Васильевич; подразделение</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Участок сборки Р</t>
+          <t>Слесарный участок Р</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>Участок сборки</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7665,22 +7665,22 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.318, Зайцев Дмитрий Евгеньевич; подразделение</t>
+          <t>Учёт, стр.315, Козлов Алексей Викторович; подразделение</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Участок сборки Р</t>
+          <t>Слесарный участок Р</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>Участок сборки</t>
+          <t>Слесарный участок</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.319, Мартынов Гавриил Викторович; подразделение</t>
+          <t>Учёт, стр.316, Чепуштанов Александр Геннадьевич; подразделение</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.320, Николаев Никита Андреевич; подразделение</t>
+          <t>Учёт, стр.317, Житников Андрей Николаевич; подразделение</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.321, Бузаев Дмитрий Анатольевич; подразделение</t>
+          <t>Учёт, стр.318, Зайцев Дмитрий Евгеньевич; подразделение</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.322, Еремеев Сергей Анатольевич; подразделение</t>
+          <t>Учёт, стр.319, Мартынов Гавриил Викторович; подразделение</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.323, Балковский Сергей Вадимович; подразделение</t>
+          <t>Учёт, стр.320, Николаев Никита Андреевич; подразделение</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.324, Гурьянов Евгений Николаевич; подразделение</t>
+          <t>Учёт, стр.321, Бузаев Дмитрий Анатольевич; подразделение</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -7872,7 +7872,7 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.325, Зайцев Евгений Геннадьевич; подразделение</t>
+          <t>Учёт, стр.322, Еремеев Сергей Анатольевич; подразделение</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.326, Швецов Андрей Витальевич; подразделение</t>
+          <t>Учёт, стр.323, Балковский Сергей Вадимович; подразделение</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7953,22 +7953,22 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.327, Богатырева Наталья Геннадьевна; подразделение</t>
+          <t>Учёт, стр.324, Гурьянов Евгений Николаевич; подразделение</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Швейный участок Р</t>
+          <t>Участок сборки Р</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>Швейный участок</t>
+          <t>Участок сборки</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -7985,22 +7985,22 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.328, Большаков Сергей Александрович; подразделение</t>
+          <t>Учёт, стр.325, Зайцев Евгений Геннадьевич; подразделение</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Швейный участок Р</t>
+          <t>Участок сборки Р</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>Швейный участок</t>
+          <t>Участок сборки</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8017,22 +8017,22 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.329, Долженко Ольга Васильевна; подразделение</t>
+          <t>Учёт, стр.326, Швецов Андрей Витальевич; подразделение</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Швейный участок Р</t>
+          <t>Участок сборки Р</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>Швейный участок</t>
+          <t>Участок сборки</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.330, Кульков Павел Петрович; подразделение</t>
+          <t>Учёт, стр.327, Богатырева Наталья Геннадьевна; подразделение</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.331, Путилина Ирина Михайловна; подразделение</t>
+          <t>Учёт, стр.328, Большаков Сергей Александрович; подразделение</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.332, Андрякова Надежда Дмитриевна; подразделение</t>
+          <t>Учёт, стр.329, Долженко Ольга Васильевна; подразделение</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.333, Антонова Елена Анатольевна; подразделение</t>
+          <t>Учёт, стр.330, Кульков Павел Петрович; подразделение</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.334, Ахмедов Яшар Закир Оглы; подразделение</t>
+          <t>Учёт, стр.331, Путилина Ирина Михайловна; подразделение</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.335, Долматова Екатерина Владимировна; подразделение</t>
+          <t>Учёт, стр.332, Андрякова Надежда Дмитриевна; подразделение</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8241,7 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.336, Китаева Венера Минигалеевна; подразделение</t>
+          <t>Учёт, стр.333, Антонова Елена Анатольевна; подразделение</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.337, Пичугина Оксана Валерьевна; подразделение</t>
+          <t>Учёт, стр.334, Ахмедов Яшар Закир Оглы; подразделение</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.338, Треусов Сергей Юрьевич; подразделение</t>
+          <t>Учёт, стр.335, Долматова Екатерина Владимировна; подразделение</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8337,7 +8337,7 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.339, Горбушина Венера Энверовна; подразделение</t>
+          <t>Учёт, стр.336, Китаева Венера Минигалеевна; подразделение</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.340, Кулешова Виктория Викторовна; подразделение</t>
+          <t>Учёт, стр.337, Пичугина Оксана Валерьевна; подразделение</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8401,7 +8401,7 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.341, Зайцев Антон Валерьевич; подразделение</t>
+          <t>Учёт, стр.338, Треусов Сергей Юрьевич; подразделение</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8433,22 +8433,22 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.342, Сабирова Альфия Фаузиевна; подразделение</t>
+          <t>Учёт, стр.339, Горбушина Венера Энверовна; подразделение</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел Р</t>
+          <t>Швейный участок Р</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел</t>
+          <t>Швейный участок</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8465,22 +8465,22 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.343, Стребкова Наталья Ивановна; подразделение</t>
+          <t>Учёт, стр.340, Кулешова Виктория Викторовна; подразделение</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел Р</t>
+          <t>Швейный участок Р</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел</t>
+          <t>Швейный участок</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8497,22 +8497,22 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.344, Оболонина Ирина Валерьевна; подразделение</t>
+          <t>Учёт, стр.341, Зайцев Антон Валерьевич; подразделение</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел Р</t>
+          <t>Швейный участок Р</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>Планово-диспетчерский отдел</t>
+          <t>Швейный участок</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8529,7 +8529,7 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.345, Яковлева Анастасия Юрьевна; подразделение</t>
+          <t>Учёт, стр.342, Сабирова Альфия Фаузиевна; подразделение</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.346, Решилова Юлия Евгеньевна; подразделение</t>
+          <t>Учёт, стр.343, Стребкова Наталья Ивановна; подразделение</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8593,22 +8593,22 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.347, Юдина Анна Владимировна; подразделение</t>
+          <t>Учёт, стр.344, Оболонина Ирина Валерьевна; подразделение</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Склад Р</t>
+          <t>Планово-диспетчерский отдел Р</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>Склад</t>
+          <t>Планово-диспетчерский отдел</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8625,22 +8625,22 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.348, Садыгова Елена Васильевна; подразделение</t>
+          <t>Учёт, стр.345, Яковлева Анастасия Юрьевна; подразделение</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Склад Р</t>
+          <t>Планово-диспетчерский отдел Р</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>Склад</t>
+          <t>Планово-диспетчерский отдел</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8657,22 +8657,22 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.349, Трофимов Максим Михайлович; подразделение</t>
+          <t>Учёт, стр.346, Решилова Юлия Евгеньевна; подразделение</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Склад Р</t>
+          <t>Планово-диспетчерский отдел Р</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>Склад</t>
+          <t>Планово-диспетчерский отдел</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8689,7 +8689,7 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.350, Гагарин Алексей Владимирович; подразделение</t>
+          <t>Учёт, стр.347, Юдина Анна Владимировна; подразделение</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.351, Иванов Дмитрий Сергеевич; подразделение</t>
+          <t>Учёт, стр.348, Садыгова Елена Васильевна; подразделение</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.352, Поляков Александр Валентинович; подразделение</t>
+          <t>Учёт, стр.349, Трофимов Максим Михайлович; подразделение</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8785,22 +8785,22 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.353, Козлов Никита Андреевич; подразделение</t>
+          <t>Учёт, стр.350, Гагарин Алексей Владимирович; подразделение</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Отдел технического контроля Р</t>
+          <t>Склад Р</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>Отдел технического контроля</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8817,22 +8817,22 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.354, Милованов Александр Сергеевич; подразделение</t>
+          <t>Учёт, стр.351, Иванов Дмитрий Сергеевич; подразделение</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Отдел технического контроля Р</t>
+          <t>Склад Р</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>Отдел технического контроля</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8849,22 +8849,22 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.355, Елсуков Имант Арьевич; подразделение</t>
+          <t>Учёт, стр.352, Поляков Александр Валентинович; подразделение</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Отдел технического контроля Р</t>
+          <t>Склад Р</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>Отдел технического контроля</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8881,22 +8881,22 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.361, Картузов Павел Борисович; подразделение</t>
+          <t>Учёт, стр.353, Козлов Никита Андреевич; подразделение</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Отдел технического контроля Р</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>Мебельный участок</t>
+          <t>Отдел технического контроля</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8913,22 +8913,22 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.362, Кляцкин Антон Борисович; подразделение</t>
+          <t>Учёт, стр.354, Милованов Александр Сергеевич; подразделение</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Отдел технического контроля Р</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>Мебельный участок</t>
+          <t>Отдел технического контроля</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8945,22 +8945,22 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.363, Вавилин Артур Александрович; подразделение</t>
+          <t>Учёт, стр.355, Елсуков Имант Арьевич; подразделение</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Мебельный участок МШ</t>
+          <t>Отдел технического контроля Р</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>Мебельный участок</t>
+          <t>Отдел технического контроля</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -8977,7 +8977,7 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.364, Котов Кирилл Олегович; подразделение</t>
+          <t>Учёт, стр.361, Картузов Павел Борисович; подразделение</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -9009,22 +9009,22 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.365, Каретников Роман Григорьевич; подразделение</t>
+          <t>Учёт, стр.362, Кляцкин Антон Борисович; подразделение</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки МШ</t>
+          <t>Мебельный участок МШ</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>Участок декоративной отделки</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -9041,22 +9041,22 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.366, Дубинкин Александр Сергеевич; подразделение</t>
+          <t>Учёт, стр.363, Вавилин Артур Александрович; подразделение</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Мебельный участок МШ</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>Механический участок</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -9073,22 +9073,22 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.367, Иванов Юрий Сергеевич; подразделение</t>
+          <t>Учёт, стр.364, Котов Кирилл Олегович; подразделение</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Мебельный участок МШ</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>Механический участок</t>
+          <t>Мебельный участок</t>
         </is>
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -9105,22 +9105,22 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.368, Серебреников Артем Андреевич; подразделение</t>
+          <t>Учёт, стр.365, Каретников Роман Григорьевич; подразделение</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Механический участок МШ</t>
+          <t>Участок декоративной отделки МШ</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>Механический участок</t>
+          <t>Участок декоративной отделки</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -9137,22 +9137,22 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.369, Тверитин Сергей Алексеевич; подразделение</t>
+          <t>Учёт, стр.366, Дубинкин Александр Сергеевич; подразделение</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Служба главного инженера Р</t>
+          <t>Механический участок МШ</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>Служба главного инженера</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -9169,118 +9169,118 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Учёт, стр.370, Коровин Сергей Юрьевич; подразделение</t>
+          <t>Учёт, стр.367, Иванов Юрий Сергеевич; подразделение</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Склад Р</t>
+          <t>Механический участок МШ</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>Склад</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «Р», «МШ», «(МШ н/д)» убрано по решению ОТиПБ</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>1а. Учёт (ред. до сверки) → Учёт (после сверки): сохранность дат осмотров и формул</t>
+          <t>1. Штатка 19.10.2026 → Учёт медосмотров</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>Изменено по решению ОТиПБ</t>
+          <t>Изменена форма записи</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>Учёт, I245, Акимов Михаил Александрович</t>
+          <t>Учёт, стр.368, Серебреников Артем Андреевич; подразделение</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>п.18 (по Перечню)</t>
+          <t>Механический участок МШ</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>п.18.2</t>
+          <t>Механический участок</t>
         </is>
       </c>
       <c r="F247" s="2" t="inlineStr">
         <is>
-          <t>подпункт п.18 по категории ВУ, решение от 19.10.2026</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>1а. Учёт (ред. до сверки) → Учёт (после сверки): сохранность дат осмотров и формул</t>
+          <t>1. Штатка 19.10.2026 → Учёт медосмотров</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Изменено по решению ОТиПБ</t>
+          <t>Изменена форма записи</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Учёт, I246, Батуревич Юрий Викторович</t>
+          <t>Учёт, стр.369, Тверитин Сергей Алексеевич; подразделение</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>п.18 (по Перечню)</t>
+          <t>Служба главного инженера Р</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>п.18.1</t>
+          <t>Служба главного инженера</t>
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
-          <t>подпункт п.18 по категории ВУ, решение от 19.10.2026</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>1а. Учёт (ред. до сверки) → Учёт (после сверки): сохранность дат осмотров и формул</t>
+          <t>1. Штатка 19.10.2026 → Учёт медосмотров</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>Изменено по решению ОТиПБ</t>
+          <t>Изменена форма записи</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Учёт, I247, Василенко Александр Иванович</t>
+          <t>Учёт, стр.370, Коровин Сергей Юрьевич; подразделение</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>п.18 (по Перечню)</t>
+          <t>Склад Р</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>п.18.1</t>
+          <t>Склад</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t>подпункт п.18 по категории ВУ, решение от 19.10.2026</t>
+          <t>обозначение площадки «Р», «МШ», «(МШ н/д)», «М» убрано по решению ОТиПБ</t>
         </is>
       </c>
     </row>
@@ -9297,7 +9297,7 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Учёт, I248, Грязнов Анатолий Николаевич</t>
+          <t>Учёт, I245, Акимов Михаил Александрович</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Учёт, I249, Евдокимов Игорь Валентинович</t>
+          <t>Учёт, I246, Батуревич Юрий Викторович</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Учёт, I250, Ерофеев Олег Игоревич</t>
+          <t>Учёт, I247, Василенко Александр Иванович</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Учёт, I251, Жигунов Вячеслав Владимирович</t>
+          <t>Учёт, I248, Грязнов Анатолий Николаевич</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Учёт, I252, Крутяков Сергей Владимирович</t>
+          <t>Учёт, I249, Евдокимов Игорь Валентинович</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>Учёт, I253, Лучкин Евгений Иванович</t>
+          <t>Учёт, I250, Ерофеев Олег Игоревич</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -9479,96 +9479,96 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>4. Шаблон ЛМК → Приказ о ПМО</t>
+          <t>1а. Учёт (ред. до сверки) → Учёт (после сверки): сохранность дат осмотров и формул</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Изменена форма записи</t>
+          <t>Изменено по решению ОТиПБ</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 1, Болденкова Анна Сергеевна; пункты 29н</t>
+          <t>Учёт, I251, Жигунов Вячеслав Владимирович</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>п.1.48, п.4.4, п.5.1</t>
+          <t>п.18 (по Перечню)</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>1.48, 4.4, 5.1</t>
+          <t>п.18.2</t>
         </is>
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>приставка «п.» не переносится — по образцу загруженной редакции приказа</t>
+          <t>подпункт п.18 по категории ВУ, решение от 19.10.2026</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>4. Шаблон ЛМК → Приказ о ПМО</t>
+          <t>1а. Учёт (ред. до сверки) → Учёт (после сверки): сохранность дат осмотров и формул</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>Изменена форма записи</t>
+          <t>Изменено по решению ОТиПБ</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 2, Иванова Светлана Васильевна; пункты 29н</t>
+          <t>Учёт, I252, Крутяков Сергей Владимирович</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>п.1.48, п.4.4, п.5.1</t>
+          <t>п.18 (по Перечню)</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>1.48, 4.4, 5.1</t>
+          <t>п.18.1</t>
         </is>
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t>приставка «п.» не переносится — по образцу загруженной редакции приказа</t>
+          <t>подпункт п.18 по категории ВУ, решение от 19.10.2026</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>4. Шаблон ЛМК → Приказ о ПМО</t>
+          <t>1а. Учёт (ред. до сверки) → Учёт (после сверки): сохранность дат осмотров и формул</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Изменена форма записи</t>
+          <t>Изменено по решению ОТиПБ</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 3, Терешкина Татьяна Викторовна; пункты 29н</t>
+          <t>Учёт, I253, Лучкин Евгений Иванович</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>п.1.48, п.4.4, п.5.1</t>
+          <t>п.18 (по Перечню)</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>1.48, 4.4, 5.1</t>
+          <t>п.18.1</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
-          <t>приставка «п.» не переносится — по образцу загруженной редакции приказа</t>
+          <t>подпункт п.18 по категории ВУ, решение от 19.10.2026</t>
         </is>
       </c>
     </row>
@@ -9585,7 +9585,7 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 4, Шибатина Елена Васильевна; пункты 29н</t>
+          <t>Приложение № 1, № 1, Болденкова Анна Сергеевна; пункты 29н</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
@@ -9617,17 +9617,17 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 5, Андреев Кирилл Владимирович; пункты 29н</t>
+          <t>Приложение № 1, № 2, Иванова Светлана Васильевна; пункты 29н</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+          <t>п.1.48, п.4.4, п.5.1</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
+          <t>1.48, 4.4, 5.1</t>
         </is>
       </c>
       <c r="F260" s="2" t="inlineStr">
@@ -9649,17 +9649,17 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 6, Воркунов Егор Дмитриевич; пункты 29н</t>
+          <t>Приложение № 1, № 3, Терешкина Татьяна Викторовна; пункты 29н</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+          <t>п.1.48, п.4.4, п.5.1</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
+          <t>1.48, 4.4, 5.1</t>
         </is>
       </c>
       <c r="F261" s="2" t="inlineStr">
@@ -9681,17 +9681,17 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 7, Герасимов Александр Александрович; пункты 29н</t>
+          <t>Приложение № 1, № 4, Шибатина Елена Васильевна; пункты 29н</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+          <t>п.1.48, п.4.4, п.5.1</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
+          <t>1.48, 4.4, 5.1</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 8, Геращенко Сергей Владимирович; пункты 29н</t>
+          <t>Приложение № 1, № 5, Андреев Кирилл Владимирович; пункты 29н</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 9, Горнеев Никита Сергеевич; пункты 29н</t>
+          <t>Приложение № 1, № 6, Воркунов Егор Дмитриевич; пункты 29н</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 10, Кашкаров Сергей Евгеньевич; пункты 29н</t>
+          <t>Приложение № 1, № 7, Герасимов Александр Александрович; пункты 29н</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 11, Куликов Сергей Сергеевич; пункты 29н</t>
+          <t>Приложение № 1, № 8, Геращенко Сергей Владимирович; пункты 29н</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 12, Павозков Евгений Александрович; пункты 29н</t>
+          <t>Приложение № 1, № 9, Горнеев Никита Сергеевич; пункты 29н</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 13, Пак Игорь Трофимович; пункты 29н</t>
+          <t>Приложение № 1, № 10, Кашкаров Сергей Евгеньевич; пункты 29н</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 14, Панков Иван Валерьевич; пункты 29н</t>
+          <t>Приложение № 1, № 11, Куликов Сергей Сергеевич; пункты 29н</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 15, Поливанов Иван Юрьевич; пункты 29н</t>
+          <t>Приложение № 1, № 12, Павозков Евгений Александрович; пункты 29н</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 16, Семячко Константин Григорьевич; пункты 29н</t>
+          <t>Приложение № 1, № 13, Пак Игорь Трофимович; пункты 29н</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 17, Янышев Тимур Ильгизович; пункты 29н</t>
+          <t>Приложение № 1, № 14, Панков Иван Валерьевич; пункты 29н</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
@@ -10033,17 +10033,17 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 18, Милованов Александр Сергеевич; пункты 29н</t>
+          <t>Приложение № 1, № 15, Поливанов Иван Юрьевич; пункты 29н</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>4.4, 5.2</t>
+          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
         </is>
       </c>
       <c r="F273" s="2" t="inlineStr">
@@ -10065,17 +10065,17 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 19, Оболонина Ирина Валерьевна; пункты 29н</t>
+          <t>Приложение № 1, № 16, Семячко Константин Григорьевич; пункты 29н</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>4.4, 5.2</t>
+          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
         </is>
       </c>
       <c r="F274" s="2" t="inlineStr">
@@ -10097,17 +10097,17 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 20, Рузайкин Юрий Андреевич; пункты 29н</t>
+          <t>Приложение № 1, № 17, Янышев Тимур Ильгизович; пункты 29н</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>4.4, 5.2</t>
+          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
         </is>
       </c>
       <c r="F275" s="2" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 21, Стребкова Наталья Ивановна; пункты 29н</t>
+          <t>Приложение № 1, № 18, Милованов Александр Сергеевич; пункты 29н</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 22, Яковлева Анастасия Юрьевна; пункты 29н</t>
+          <t>Приложение № 1, № 19, Оболонина Ирина Валерьевна; пункты 29н</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
@@ -10193,17 +10193,17 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 23, Садыгова Елена Васильевна; пункты 29н</t>
+          <t>Приложение № 1, № 20, Рузайкин Юрий Андреевич; пункты 29н</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.6.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>4.4, 5.1, 6.2</t>
+          <t>4.4, 5.2</t>
         </is>
       </c>
       <c r="F278" s="2" t="inlineStr">
@@ -10225,17 +10225,17 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 24, Юдина Анна Владимировна; пункты 29н</t>
+          <t>Приложение № 1, № 21, Стребкова Наталья Ивановна; пункты 29н</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.6.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>4.4, 5.1, 6.2</t>
+          <t>4.4, 5.2</t>
         </is>
       </c>
       <c r="F279" s="2" t="inlineStr">
@@ -10257,17 +10257,17 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 25, Баев Сергей Александрович; пункты 29н</t>
+          <t>Приложение № 1, № 22, Яковлева Анастасия Юрьевна; пункты 29н</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>4.3.1, 4.3.2, 4.4, 5.1, 15</t>
+          <t>4.4, 5.2</t>
         </is>
       </c>
       <c r="F280" s="2" t="inlineStr">
@@ -10289,17 +10289,17 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 26, Гришин Алексей Валерьевич; пункты 29н</t>
+          <t>Приложение № 1, № 23, Садыгова Елена Васильевна; пункты 29н</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.4.4, п.5.1, п.6.2</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>4.3.1, 4.3.2, 4.4, 5.1, 15</t>
+          <t>4.4, 5.1, 6.2</t>
         </is>
       </c>
       <c r="F281" s="2" t="inlineStr">
@@ -10321,17 +10321,17 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 27, Козлов Алексей Викторович; пункты 29н</t>
+          <t>Приложение № 1, № 24, Юдина Анна Владимировна; пункты 29н</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.4.4, п.5.1, п.6.2</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>4.3.1, 4.3.2, 4.4, 5.1, 15</t>
+          <t>4.4, 5.1, 6.2</t>
         </is>
       </c>
       <c r="F282" s="2" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 28, Корнеев Виктор Николаевич; пункты 29н</t>
+          <t>Приложение № 1, № 25, Баев Сергей Александрович; пункты 29н</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 29, Федышен Валерий Васильевич; пункты 29н</t>
+          <t>Приложение № 1, № 26, Гришин Алексей Валерьевич; пункты 29н</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
@@ -10417,17 +10417,17 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 30, Балковский Сергей Вадимович; пункты 29н</t>
+          <t>Приложение № 1, № 27, Козлов Алексей Викторович; пункты 29н</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.15</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>4.3.1, 4.3.2, 4.4, 5.1, 6.2, 15</t>
+          <t>4.3.1, 4.3.2, 4.4, 5.1, 15</t>
         </is>
       </c>
       <c r="F285" s="2" t="inlineStr">
@@ -10449,17 +10449,17 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 31, Бузаев Дмитрий Анатольевич; пункты 29н</t>
+          <t>Приложение № 1, № 28, Корнеев Виктор Николаевич; пункты 29н</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.15</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>4.3.1, 4.3.2, 4.4, 5.1, 6.2, 15</t>
+          <t>4.3.1, 4.3.2, 4.4, 5.1, 15</t>
         </is>
       </c>
       <c r="F286" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 32, Гурьянов Евгений Николаевич; пункты 29н</t>
+          <t>Приложение № 1, № 29, Федышен Валерий Васильевич; пункты 29н</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.15</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>4.3.1, 4.3.2, 4.4, 5.1, 6.2, 15</t>
+          <t>4.3.1, 4.3.2, 4.4, 5.1, 15</t>
         </is>
       </c>
       <c r="F287" s="2" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 33, Еремеев Сергей Анатольевич; пункты 29н</t>
+          <t>Приложение № 1, № 30, Балковский Сергей Вадимович; пункты 29н</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
@@ -10545,7 +10545,7 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 34, Житников Андрей Николаевич; пункты 29н</t>
+          <t>Приложение № 1, № 31, Бузаев Дмитрий Анатольевич; пункты 29н</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 35, Зайцев Дмитрий Евгеньевич; пункты 29н</t>
+          <t>Приложение № 1, № 32, Гурьянов Евгений Николаевич; пункты 29н</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 36, Зайцев Евгений Геннадьевич; пункты 29н</t>
+          <t>Приложение № 1, № 33, Еремеев Сергей Анатольевич; пункты 29н</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 37, Николаев Никита Андреевич; пункты 29н</t>
+          <t>Приложение № 1, № 34, Житников Андрей Николаевич; пункты 29н</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
@@ -10673,7 +10673,7 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 38, Чепуштанов Александр Геннадьевич; пункты 29н</t>
+          <t>Приложение № 1, № 35, Зайцев Дмитрий Евгеньевич; пункты 29н</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
@@ -10705,7 +10705,7 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 39, Швецов Андрей Витальевич; пункты 29н</t>
+          <t>Приложение № 1, № 36, Зайцев Евгений Геннадьевич; пункты 29н</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
@@ -10737,17 +10737,17 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 40, Андрякова Надежда Дмитриевна; пункты 29н</t>
+          <t>Приложение № 1, № 37, Николаев Никита Андреевич; пункты 29н</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.15</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
+          <t>4.3.1, 4.3.2, 4.4, 5.1, 6.2, 15</t>
         </is>
       </c>
       <c r="F295" s="2" t="inlineStr">
@@ -10769,17 +10769,17 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 41, Антонова Елена Анатольевна; пункты 29н</t>
+          <t>Приложение № 1, № 38, Чепуштанов Александр Геннадьевич; пункты 29н</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.15</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>4.4, 5.2</t>
+          <t>4.3.1, 4.3.2, 4.4, 5.1, 6.2, 15</t>
         </is>
       </c>
       <c r="F296" s="2" t="inlineStr">
@@ -10801,17 +10801,17 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 42, Ахмедов Яшар Закир Оглы; пункты 29н</t>
+          <t>Приложение № 1, № 39, Швецов Андрей Витальевич; пункты 29н</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.15</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
+          <t>4.3.1, 4.3.2, 4.4, 5.1, 6.2, 15</t>
         </is>
       </c>
       <c r="F297" s="2" t="inlineStr">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 43, Богатырева Наталья Геннадьевна; пункты 29н</t>
+          <t>Приложение № 1, № 40, Андрякова Надежда Дмитриевна; пункты 29н</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
@@ -10865,17 +10865,17 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 44, Большаков Сергей Александрович; пункты 29н</t>
+          <t>Приложение № 1, № 41, Антонова Елена Анатольевна; пункты 29н</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
+          <t>4.4, 5.2</t>
         </is>
       </c>
       <c r="F299" s="2" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 45, Горбушина Венера Энверовна; пункты 29н</t>
+          <t>Приложение № 1, № 42, Ахмедов Яшар Закир Оглы; пункты 29н</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 46, Долженко Ольга Васильевна; пункты 29н</t>
+          <t>Приложение № 1, № 43, Богатырева Наталья Геннадьевна; пункты 29н</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 47, Долматова Екатерина Владимировна; пункты 29н</t>
+          <t>Приложение № 1, № 44, Большаков Сергей Александрович; пункты 29н</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
@@ -10993,7 +10993,7 @@
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 48, Китаева Венера Минигалеевна; пункты 29н</t>
+          <t>Приложение № 1, № 45, Горбушина Венера Энверовна; пункты 29н</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 49, Кулешова Виктория Викторовна; пункты 29н</t>
+          <t>Приложение № 1, № 46, Долженко Ольга Васильевна; пункты 29н</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 50, Кульков Павел Петрович; пункты 29н</t>
+          <t>Приложение № 1, № 47, Долматова Екатерина Владимировна; пункты 29н</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
@@ -11089,7 +11089,7 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 51, Пичугина Оксана Валерьевна; пункты 29н</t>
+          <t>Приложение № 1, № 48, Китаева Венера Минигалеевна; пункты 29н</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 52, Путилина Ирина Михайловна; пункты 29н</t>
+          <t>Приложение № 1, № 49, Кулешова Виктория Викторовна; пункты 29н</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 1, № 53, Треусов Сергей Юрьевич; пункты 29н</t>
+          <t>Приложение № 1, № 50, Кульков Павел Петрович; пункты 29н</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
@@ -11185,17 +11185,17 @@
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 1, Гросс Елена Владимировна; пункты 29н</t>
+          <t>Приложение № 1, № 51, Пичугина Оксана Валерьевна; пункты 29н</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>п.1.48, п.4.4, п.5.1</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>1.48, 4.4, 5.1</t>
+          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
         </is>
       </c>
       <c r="F309" s="2" t="inlineStr">
@@ -11217,17 +11217,17 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 2, Декун Лидия Петровна; пункты 29н</t>
+          <t>Приложение № 1, № 52, Путилина Ирина Михайловна; пункты 29н</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>п.1.48, п.4.4, п.5.1</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>1.48, 4.4, 5.1</t>
+          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
         </is>
       </c>
       <c r="F310" s="2" t="inlineStr">
@@ -11249,17 +11249,17 @@
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 3, Захарова Любовь Владимировна; пункты 29н</t>
+          <t>Приложение № 1, № 53, Треусов Сергей Юрьевич; пункты 29н</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>4.4, 5.2</t>
+          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
         </is>
       </c>
       <c r="F311" s="2" t="inlineStr">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 4, Михеева Наталия Петровна; пункты 29н</t>
+          <t>Приложение № 2, № 1, Гросс Елена Владимировна; пункты 29н</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
@@ -11313,7 +11313,7 @@
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 5, Новоторцева Наталия Николаевна; пункты 29н</t>
+          <t>Приложение № 2, № 2, Декун Лидия Петровна; пункты 29н</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
@@ -11345,17 +11345,17 @@
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 6, Савичева Марина Анатольевна; пункты 29н</t>
+          <t>Приложение № 2, № 3, Захарова Любовь Владимировна; пункты 29н</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>п.1.48, п.4.4, п.5.1</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>1.48, 4.4, 5.1</t>
+          <t>4.4, 5.2</t>
         </is>
       </c>
       <c r="F314" s="2" t="inlineStr">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 7, Хилинская Анна Александровна; пункты 29н</t>
+          <t>Приложение № 2, № 4, Михеева Наталия Петровна; пункты 29н</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
@@ -11409,17 +11409,17 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 8, Алманов Вячеслав Михайлович; пункты 29н</t>
+          <t>Приложение № 2, № 5, Новоторцева Наталия Николаевна; пункты 29н</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.1.48, п.4.4, п.5.1</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>1.49.2, 1.49.14, 4.3.1, 4.3.2, 4.4, 5.1, 15</t>
+          <t>1.48, 4.4, 5.1</t>
         </is>
       </c>
       <c r="F316" s="2" t="inlineStr">
@@ -11441,17 +11441,17 @@
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 9, Анисимов Игорь Владимирович; пункты 29н</t>
+          <t>Приложение № 2, № 6, Савичева Марина Анатольевна; пункты 29н</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>п.1.37.1, п.3.1.8.3, п.4.3.1, п.4.4, п.5.1, п.15</t>
+          <t>п.1.48, п.4.4, п.5.1</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>1.37.1, 3.1.8.3, 4.3.1, 4.4, 5.1, 15</t>
+          <t>1.48, 4.4, 5.1</t>
         </is>
       </c>
       <c r="F317" s="2" t="inlineStr">
@@ -11473,17 +11473,17 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 10, Анненков Олег Викторович; пункты 29н</t>
+          <t>Приложение № 2, № 7, Хилинская Анна Александровна; пункты 29н</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.1.48, п.4.4, п.5.1</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>1.49.2, 1.49.14, 4.3.1, 4.3.2, 4.4, 5.1, 15</t>
+          <t>1.48, 4.4, 5.1</t>
         </is>
       </c>
       <c r="F318" s="2" t="inlineStr">
@@ -11505,17 +11505,17 @@
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 11, Антропов Иван Юрьевич; пункты 29н</t>
+          <t>Приложение № 2, № 8, Алманов Вячеслав Михайлович; пункты 29н</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>п.1.37.1, п.3.1.8.3, п.4.3.1, п.4.4, п.5.1, п.15</t>
+          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>1.37.1, 3.1.8.3, 4.3.1, 4.4, 5.1, 15</t>
+          <t>1.49.2, 1.49.14, 4.3.1, 4.3.2, 4.4, 5.1, 15</t>
         </is>
       </c>
       <c r="F319" s="2" t="inlineStr">
@@ -11537,17 +11537,17 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 12, Арифулин Александр Александрович; пункты 29н</t>
+          <t>Приложение № 2, № 9, Анисимов Игорь Владимирович; пункты 29н</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.1.37.1, п.3.1.8.3, п.4.3.1, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>1.49.2, 1.49.14, 4.3.1, 4.3.2, 4.4, 5.1, 15</t>
+          <t>1.37.1, 3.1.8.3, 4.3.1, 4.4, 5.1, 15</t>
         </is>
       </c>
       <c r="F320" s="2" t="inlineStr">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 13, Бабенко Олег Анатольевич; пункты 29н</t>
+          <t>Приложение № 2, № 10, Анненков Олег Викторович; пункты 29н</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 14, Балалаев Сергей Викторович; пункты 29н</t>
+          <t>Приложение № 2, № 11, Антропов Иван Юрьевич; пункты 29н</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
@@ -11633,17 +11633,17 @@
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 15, Бредихин Евгений Васильевич; пункты 29н</t>
+          <t>Приложение № 2, № 12, Арифулин Александр Александрович; пункты 29н</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>п.1.37.1, п.3.1.8.3, п.4.3.1, п.4.4, п.5.1, п.15</t>
+          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>1.37.1, 3.1.8.3, 4.3.1, 4.4, 5.1, 15</t>
+          <t>1.49.2, 1.49.14, 4.3.1, 4.3.2, 4.4, 5.1, 15</t>
         </is>
       </c>
       <c r="F323" s="2" t="inlineStr">
@@ -11665,17 +11665,17 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 16, Бутузов Вадим Владимирович; пункты 29н</t>
+          <t>Приложение № 2, № 13, Бабенко Олег Анатольевич; пункты 29н</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
+          <t>1.49.2, 1.49.14, 4.3.1, 4.3.2, 4.4, 5.1, 15</t>
         </is>
       </c>
       <c r="F324" s="2" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 17, Ветлянский Александр Александрович; пункты 29н</t>
+          <t>Приложение № 2, № 14, Балалаев Сергей Викторович; пункты 29н</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
@@ -11729,17 +11729,17 @@
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 18, Зайцев Андрей Александрович; пункты 29н</t>
+          <t>Приложение № 2, № 15, Бредихин Евгений Васильевич; пункты 29н</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.1.37.1, п.3.1.8.3, п.4.3.1, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>1.49.2, 1.49.14, 4.3.1, 4.3.2, 4.4, 5.1, 15</t>
+          <t>1.37.1, 3.1.8.3, 4.3.1, 4.4, 5.1, 15</t>
         </is>
       </c>
       <c r="F326" s="2" t="inlineStr">
@@ -11761,17 +11761,17 @@
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 19, Захаров Юрий Викторович; пункты 29н</t>
+          <t>Приложение № 2, № 16, Бутузов Вадим Владимирович; пункты 29н</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>1.49.2, 1.49.14, 4.3.1, 4.3.2, 4.4, 5.1, 15</t>
+          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
         </is>
       </c>
       <c r="F327" s="2" t="inlineStr">
@@ -11793,17 +11793,17 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 20, Кляцкин Антон Борисович; пункты 29н</t>
+          <t>Приложение № 2, № 17, Ветлянский Александр Александрович; пункты 29н</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.1.37.1, п.3.1.8.3, п.4.3.1, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>1.49.2, 1.49.14, 4.3.1, 4.3.2, 4.4, 5.1, 15</t>
+          <t>1.37.1, 3.1.8.3, 4.3.1, 4.4, 5.1, 15</t>
         </is>
       </c>
       <c r="F328" s="2" t="inlineStr">
@@ -11825,7 +11825,7 @@
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 21, Кротков Александр Юрьевич; пункты 29н</t>
+          <t>Приложение № 2, № 18, Зайцев Андрей Александрович; пункты 29н</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
@@ -11857,7 +11857,7 @@
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 22, Кукушкин Дмитрий Вячеславович; пункты 29н</t>
+          <t>Приложение № 2, № 19, Захаров Юрий Викторович; пункты 29н</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
@@ -11889,17 +11889,17 @@
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 23, Кукушкин Максим Дмитриевич; пункты 29н</t>
+          <t>Приложение № 2, № 20, Кляцкин Антон Борисович; пункты 29н</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>п.1.37.1, п.3.1.8.3, п.4.3.1, п.4.4, п.5.1, п.15</t>
+          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>1.37.1, 3.1.8.3, 4.3.1, 4.4, 5.1, 15</t>
+          <t>1.49.2, 1.49.14, 4.3.1, 4.3.2, 4.4, 5.1, 15</t>
         </is>
       </c>
       <c r="F331" s="2" t="inlineStr">
@@ -11921,7 +11921,7 @@
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 24, Макарский Станислав Иванович; пункты 29н</t>
+          <t>Приложение № 2, № 21, Кротков Александр Юрьевич; пункты 29н</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
@@ -11953,7 +11953,7 @@
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 25, Малышкин Сергей Константинович; пункты 29н</t>
+          <t>Приложение № 2, № 22, Кукушкин Дмитрий Вячеславович; пункты 29н</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
@@ -11985,17 +11985,17 @@
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 26, Маркарян Роман Рубикович; пункты 29н</t>
+          <t>Приложение № 2, № 23, Кукушкин Максим Дмитриевич; пункты 29н</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.1.37.1, п.3.1.8.3, п.4.3.1, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>1.49.2, 1.49.14, 4.3.1, 4.3.2, 4.4, 5.1, 15</t>
+          <t>1.37.1, 3.1.8.3, 4.3.1, 4.4, 5.1, 15</t>
         </is>
       </c>
       <c r="F334" s="2" t="inlineStr">
@@ -12017,17 +12017,17 @@
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 27, Матухно Константин Викторович; пункты 29н</t>
+          <t>Приложение № 2, № 24, Макарский Станислав Иванович; пункты 29н</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>4.4, 5.1, 5.2</t>
+          <t>1.49.2, 1.49.14, 4.3.1, 4.3.2, 4.4, 5.1, 15</t>
         </is>
       </c>
       <c r="F335" s="2" t="inlineStr">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 28, Михиенков Валерий Евгеньевич; пункты 29н</t>
+          <t>Приложение № 2, № 25, Малышкин Сергей Константинович; пункты 29н</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
@@ -12081,17 +12081,17 @@
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 29, Морозов Олег Валерьевич; пункты 29н</t>
+          <t>Приложение № 2, № 26, Маркарян Роман Рубикович; пункты 29н</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
+          <t>1.49.2, 1.49.14, 4.3.1, 4.3.2, 4.4, 5.1, 15</t>
         </is>
       </c>
       <c r="F337" s="2" t="inlineStr">
@@ -12113,17 +12113,17 @@
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 30, Мураев Вадим Викторович; пункты 29н</t>
+          <t>Приложение № 2, № 27, Матухно Константин Викторович; пункты 29н</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.4.4, п.5.1, п.5.2</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>1.49.2, 1.49.14, 4.3.1, 4.3.2, 4.4, 5.1, 15</t>
+          <t>4.4, 5.1, 5.2</t>
         </is>
       </c>
       <c r="F338" s="2" t="inlineStr">
@@ -12145,17 +12145,17 @@
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 31, Нерозников Роман Анатольевич; пункты 29н</t>
+          <t>Приложение № 2, № 28, Михиенков Валерий Евгеньевич; пункты 29н</t>
         </is>
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.2</t>
+          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>4.4, 5.2</t>
+          <t>1.49.2, 1.49.14, 4.3.1, 4.3.2, 4.4, 5.1, 15</t>
         </is>
       </c>
       <c r="F339" s="2" t="inlineStr">
@@ -12177,17 +12177,17 @@
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 32, Никитин Валерий Сергеевич; пункты 29н</t>
+          <t>Приложение № 2, № 29, Морозов Олег Валерьевич; пункты 29н</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>4.4, 5.2</t>
+          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
         </is>
       </c>
       <c r="F340" s="2" t="inlineStr">
@@ -12209,7 +12209,7 @@
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 33, Пантюхов Вячеслав Владимирович; пункты 29н</t>
+          <t>Приложение № 2, № 30, Мураев Вадим Викторович; пункты 29н</t>
         </is>
       </c>
       <c r="D341" s="2" t="inlineStr">
@@ -12241,17 +12241,17 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 34, Петушков Дмитрий Сергеевич; пункты 29н</t>
+          <t>Приложение № 2, № 31, Нерозников Роман Анатольевич; пункты 29н</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>1.49.2, 1.49.14, 4.3.1, 4.3.2, 4.4, 5.1, 15</t>
+          <t>4.4, 5.2</t>
         </is>
       </c>
       <c r="F342" s="2" t="inlineStr">
@@ -12273,17 +12273,17 @@
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 35, Пичугин Александр Владимирович; пункты 29н</t>
+          <t>Приложение № 2, № 32, Никитин Валерий Сергеевич; пункты 29н</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>п.1.37.1, п.3.1.8.3, п.4.3.1, п.4.4, п.5.1, п.15</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>1.37.1, 3.1.8.3, 4.3.1, 4.4, 5.1, 15</t>
+          <t>4.4, 5.2</t>
         </is>
       </c>
       <c r="F343" s="2" t="inlineStr">
@@ -12305,7 +12305,7 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 36, Полудкин Роман Владимирович; пункты 29н</t>
+          <t>Приложение № 2, № 33, Пантюхов Вячеслав Владимирович; пункты 29н</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 37, Рыжков Олег Николаевич; пункты 29н</t>
+          <t>Приложение № 2, № 34, Петушков Дмитрий Сергеевич; пункты 29н</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
@@ -12369,17 +12369,17 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 38, Савельев Станислав Юрьевич; пункты 29н</t>
+          <t>Приложение № 2, № 35, Пичугин Александр Владимирович; пункты 29н</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.1.37.1, п.3.1.8.3, п.4.3.1, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>1.49.2, 1.49.14, 4.3.1, 4.3.2, 4.4, 5.1, 15</t>
+          <t>1.37.1, 3.1.8.3, 4.3.1, 4.4, 5.1, 15</t>
         </is>
       </c>
       <c r="F346" s="2" t="inlineStr">
@@ -12401,7 +12401,7 @@
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 39, Селиванов Алексей Алексеевич; пункты 29н</t>
+          <t>Приложение № 2, № 36, Полудкин Роман Владимирович; пункты 29н</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
@@ -12433,7 +12433,7 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 40, Семенов Александр Александрович; пункты 29н</t>
+          <t>Приложение № 2, № 37, Рыжков Олег Николаевич; пункты 29н</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 41, Степанов Валентин Владимирович; пункты 29н</t>
+          <t>Приложение № 2, № 38, Савельев Станислав Юрьевич; пункты 29н</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
@@ -12497,17 +12497,17 @@
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 42, Тимошенко Александр Олегович; пункты 29н</t>
+          <t>Приложение № 2, № 39, Селиванов Алексей Алексеевич; пункты 29н</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>п.1.37.1, п.3.1.8.3, п.4.3.1, п.4.4, п.5.1, п.15</t>
+          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>1.37.1, 3.1.8.3, 4.3.1, 4.4, 5.1, 15</t>
+          <t>1.49.2, 1.49.14, 4.3.1, 4.3.2, 4.4, 5.1, 15</t>
         </is>
       </c>
       <c r="F350" s="2" t="inlineStr">
@@ -12529,7 +12529,7 @@
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 43, Трушков Сергей Викторович; пункты 29н</t>
+          <t>Приложение № 2, № 40, Семенов Александр Александрович; пункты 29н</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
@@ -12561,17 +12561,17 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 44, Хасянов Ильфат Шамильевич; пункты 29н</t>
+          <t>Приложение № 2, № 41, Степанов Валентин Владимирович; пункты 29н</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
+          <t>1.49.2, 1.49.14, 4.3.1, 4.3.2, 4.4, 5.1, 15</t>
         </is>
       </c>
       <c r="F352" s="2" t="inlineStr">
@@ -12593,17 +12593,17 @@
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 45, Цибин Николай Дмитриевич; пункты 29н</t>
+          <t>Приложение № 2, № 42, Тимошенко Александр Олегович; пункты 29н</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.1, п.5.2</t>
+          <t>п.1.37.1, п.3.1.8.3, п.4.3.1, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>4.4, 5.1, 5.2</t>
+          <t>1.37.1, 3.1.8.3, 4.3.1, 4.4, 5.1, 15</t>
         </is>
       </c>
       <c r="F353" s="2" t="inlineStr">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 46, Черносвитов Дмитрий Львович; пункты 29н</t>
+          <t>Приложение № 2, № 43, Трушков Сергей Викторович; пункты 29н</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
@@ -12657,17 +12657,17 @@
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 47, Шеин Андрей Геннадьевич; пункты 29н</t>
+          <t>Приложение № 2, № 44, Хасянов Ильфат Шамильевич; пункты 29н</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>1.49.2, 1.49.14, 4.3.1, 4.3.2, 4.4, 5.1, 15</t>
+          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
         </is>
       </c>
       <c r="F355" s="2" t="inlineStr">
@@ -12689,17 +12689,17 @@
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 48, Агапов Максим Владимирович; пункты 29н</t>
+          <t>Приложение № 2, № 45, Цибин Николай Дмитриевич; пункты 29н</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+          <t>п.4.4, п.5.1, п.5.2</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
+          <t>4.4, 5.1, 5.2</t>
         </is>
       </c>
       <c r="F356" s="2" t="inlineStr">
@@ -12721,17 +12721,17 @@
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 49, Артёмов Антон Анатольевич; пункты 29н</t>
+          <t>Приложение № 2, № 46, Черносвитов Дмитрий Львович; пункты 29н</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
+          <t>1.49.2, 1.49.14, 4.3.1, 4.3.2, 4.4, 5.1, 15</t>
         </is>
       </c>
       <c r="F357" s="2" t="inlineStr">
@@ -12753,17 +12753,17 @@
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 50, Бондин Денис Игоревич; пункты 29н</t>
+          <t>Приложение № 2, № 47, Шеин Андрей Геннадьевич; пункты 29н</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
+          <t>п.1.49.2, п.1.49.14, п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.15</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
+          <t>1.49.2, 1.49.14, 4.3.1, 4.3.2, 4.4, 5.1, 15</t>
         </is>
       </c>
       <c r="F358" s="2" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 51, Горелов Андрей Сергеевич; пункты 29н</t>
+          <t>Приложение № 2, № 48, Агапов Максим Владимирович; пункты 29н</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 52, Зинченко Денис Андреевич; пункты 29н</t>
+          <t>Приложение № 2, № 49, Артёмов Антон Анатольевич; пункты 29н</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 53, Клюг Андрей Эдуардович; пункты 29н</t>
+          <t>Приложение № 2, № 50, Бондин Денис Игоревич; пункты 29н</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 54, Кулешов Руслан Викторович; пункты 29н</t>
+          <t>Приложение № 2, № 51, Горелов Андрей Сергеевич; пункты 29н</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
@@ -12913,7 +12913,7 @@
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 55, Нагаев Дмитрий Александрович; пункты 29н</t>
+          <t>Приложение № 2, № 52, Зинченко Денис Андреевич; пункты 29н</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 56, Назин Владислав Сергеевич; пункты 29н</t>
+          <t>Приложение № 2, № 53, Клюг Андрей Эдуардович; пункты 29н</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 57, Орлов Михаил Юрьевич; пункты 29н</t>
+          <t>Приложение № 2, № 54, Кулешов Руслан Викторович; пункты 29н</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 58, Потапкин Илья Анатольевич; пункты 29н</t>
+          <t>Приложение № 2, № 55, Нагаев Дмитрий Александрович; пункты 29н</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 59, Птицын Юрий Юрьевич; пункты 29н</t>
+          <t>Приложение № 2, № 56, Назин Владислав Сергеевич; пункты 29н</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
@@ -13073,7 +13073,7 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 60, Саранцев Петр Дмитриевич; пункты 29н</t>
+          <t>Приложение № 2, № 57, Орлов Михаил Юрьевич; пункты 29н</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
@@ -13105,7 +13105,7 @@
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 61, Тарасов Борис Анатольевич; пункты 29н</t>
+          <t>Приложение № 2, № 58, Потапкин Илья Анатольевич; пункты 29н</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
@@ -13137,17 +13137,17 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 62, Фокина Светлана Геннадиевна; пункты 29н</t>
+          <t>Приложение № 2, № 59, Птицын Юрий Юрьевич; пункты 29н</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>4.4, 5.2</t>
+          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
         </is>
       </c>
       <c r="F370" s="2" t="inlineStr">
@@ -13169,7 +13169,7 @@
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 63, Юдаков Алексей Викторович; пункты 29н</t>
+          <t>Приложение № 2, № 60, Саранцев Петр Дмитриевич; пункты 29н</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
@@ -13201,17 +13201,17 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 64, Беспалов Виталий Анатольевич; пункты 29н</t>
+          <t>Приложение № 2, № 61, Тарасов Борис Анатольевич; пункты 29н</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>п.4.7, п.4.8, п.5.1, п.5.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>4.7, 4.8, 5.1, 5.2</t>
+          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
         </is>
       </c>
       <c r="F372" s="2" t="inlineStr">
@@ -13233,17 +13233,17 @@
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 65, Волгин Анатолий Иванович; пункты 29н</t>
+          <t>Приложение № 2, № 62, Фокина Светлана Геннадиевна; пункты 29н</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>п.4.7, п.4.8, п.5.1, п.5.2</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
         <is>
-          <t>4.7, 4.8, 5.1, 5.2</t>
+          <t>4.4, 5.2</t>
         </is>
       </c>
       <c r="F373" s="2" t="inlineStr">
@@ -13265,17 +13265,17 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 66, Гусев Александр Николаевич; пункты 29н</t>
+          <t>Приложение № 2, № 63, Юдаков Алексей Викторович; пункты 29н</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>п.4.7, п.4.8, п.5.1, п.5.2</t>
+          <t>п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.5.2, п.15</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>4.7, 4.8, 5.1, 5.2</t>
+          <t>4.3.1, 4.3.2, 4.4, 5.1, 5.2, 15</t>
         </is>
       </c>
       <c r="F374" s="2" t="inlineStr">
@@ -13297,7 +13297,7 @@
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 67, Дудукин Сергей Вячеславович; пункты 29н</t>
+          <t>Приложение № 2, № 64, Беспалов Виталий Анатольевич; пункты 29н</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 68, Звягин Евгений Иванович; пункты 29н</t>
+          <t>Приложение № 2, № 65, Волгин Анатолий Иванович; пункты 29н</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 69, Камбулатов Эсенбулат Камбулатович; пункты 29н</t>
+          <t>Приложение № 2, № 66, Гусев Александр Николаевич; пункты 29н</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 70, Макаренко Алексей Иванович; пункты 29н</t>
+          <t>Приложение № 2, № 67, Дудукин Сергей Вячеславович; пункты 29н</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
@@ -13425,7 +13425,7 @@
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 71, Матвицкий Виктор Владимирович; пункты 29н</t>
+          <t>Приложение № 2, № 68, Звягин Евгений Иванович; пункты 29н</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
@@ -13457,7 +13457,7 @@
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 72, Рукин Денис Игоревич; пункты 29н</t>
+          <t>Приложение № 2, № 69, Камбулатов Эсенбулат Камбулатович; пункты 29н</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
@@ -13489,17 +13489,17 @@
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 73, Божьева Ирина Вячеславовна; пункты 29н</t>
+          <t>Приложение № 2, № 70, Макаренко Алексей Иванович; пункты 29н</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.2</t>
+          <t>п.4.7, п.4.8, п.5.1, п.5.2</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>4.4, 5.2</t>
+          <t>4.7, 4.8, 5.1, 5.2</t>
         </is>
       </c>
       <c r="F381" s="2" t="inlineStr">
@@ -13521,17 +13521,17 @@
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 74, Васильева Алина Владимировна; пункты 29н</t>
+          <t>Приложение № 2, № 71, Матвицкий Виктор Владимирович; пункты 29н</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.2</t>
+          <t>п.4.7, п.4.8, п.5.1, п.5.2</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>4.4, 5.2</t>
+          <t>4.7, 4.8, 5.1, 5.2</t>
         </is>
       </c>
       <c r="F382" s="2" t="inlineStr">
@@ -13553,17 +13553,17 @@
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 75, Райкова Ирина Алексеевна; пункты 29н</t>
+          <t>Приложение № 2, № 72, Рукин Денис Игоревич; пункты 29н</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>п.4.4, п.5.2</t>
+          <t>п.4.7, п.4.8, п.5.1, п.5.2</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>4.4, 5.2</t>
+          <t>4.7, 4.8, 5.1, 5.2</t>
         </is>
       </c>
       <c r="F383" s="2" t="inlineStr">
@@ -13585,22 +13585,22 @@
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 76, Ермакова Наталья Васильевна; структурное подразделение</t>
+          <t>Приложение № 2, № 73, Божьева Ирина Вячеславовна; пункты 29н</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>Отдел технического контроля М</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>Отдел технического контроля</t>
+          <t>4.4, 5.2</t>
         </is>
       </c>
       <c r="F384" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «М» не переносится — по образцу загруженной редакции приказа</t>
+          <t>приставка «п.» не переносится — по образцу загруженной редакции приказа</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 76, Ермакова Наталья Васильевна; пункты 29н</t>
+          <t>Приложение № 2, № 74, Васильева Алина Владимировна; пункты 29н</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
@@ -13649,22 +13649,22 @@
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 77, Шрамко Наталья Викторовна; структурное подразделение</t>
+          <t>Приложение № 2, № 75, Ермакова Наталья Васильевна; пункты 29н</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>Отдел технического контроля М</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>Отдел технического контроля</t>
+          <t>4.4, 5.2</t>
         </is>
       </c>
       <c r="F386" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «М» не переносится — по образцу загруженной редакции приказа</t>
+          <t>приставка «п.» не переносится — по образцу загруженной редакции приказа</t>
         </is>
       </c>
     </row>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 77, Шрамко Наталья Викторовна; пункты 29н</t>
+          <t>Приложение № 2, № 76, Райкова Ирина Алексеевна; пункты 29н</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>Приложение № 2, № 78, Ястребов Александр Сергеевич; структурное подразделение</t>
+          <t>Приложение № 2, № 77, Шрамко Наталья Викторовна; пункты 29н</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>Отдел технического контроля М</t>
+          <t>п.4.4, п.5.2</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>Отдел технического контроля</t>
+          <t>4.4, 5.2</t>
         </is>
       </c>
       <c r="F388" s="2" t="inlineStr">
         <is>
-          <t>обозначение площадки «М» не переносится — по образцу загруженной редакции приказа</t>
+          <t>приставка «п.» не переносится — по образцу загруженной редакции приказа</t>
         </is>
       </c>
     </row>
